--- a/faq.xlsx
+++ b/faq.xlsx
@@ -1,30 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucianoreis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lcreis\Documents\GitHub\faq\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD83281-BCE1-4B32-8C29-EB64F156A667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="28680" yWindow="2490" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
   <si>
     <t>Categoria</t>
   </si>
@@ -33,19 +45,370 @@
   </si>
   <si>
     <t>Resposta</t>
+  </si>
+  <si>
+    <t>Acesso a Medicamentos</t>
+  </si>
+  <si>
+    <t>Como gestantes podem acessar a Enoxaparina via CIMBAHIA/CAJ?</t>
+  </si>
+  <si>
+    <t>Se o pedido for indeferido pela COAFE, a unidade deve abrir um processo SEI para o CIMBAHIA. Caso seja deferido, o processo é encaminhado à CAJ para o atendimento administrativo.</t>
+  </si>
+  <si>
+    <t>Qual a validade dos exames para solicitação de Enoxaparina para gestantes?</t>
+  </si>
+  <si>
+    <t>Os exames necessários (B-hCG, ultrassom, hemograma, creatinina, entre outros) devem possuir validade de, no máximo, 3 meses.</t>
+  </si>
+  <si>
+    <t>Aquisição de Medicamentos</t>
+  </si>
+  <si>
+    <t>Como devem ser feitas as aquisições para pacientes judiciais e administrativos na CAJ?</t>
+  </si>
+  <si>
+    <t>As aquisições por dispensa de licitação devem ser realizadas de forma separada. Processos conduzidos por Registro de Preços (RP) ativo seguem a rotina habitual, sem necessidade de distinção entre as esferas.</t>
+  </si>
+  <si>
+    <t>Qual o critério de tempo de validade para aceitação de medicamentos entregues por fornecedores?</t>
+  </si>
+  <si>
+    <t>No ato da entrega, não poderá ter transcorrido mais de 20% do prazo total de validade a partir da data de fabricação. Editais da CAJ exigem que a validade remanescente seja igual ou superior a 1 ano.</t>
+  </si>
+  <si>
+    <t>Qual o tempo de ressuprimento estimado para itens de Registro de Preços e Dispensas?</t>
+  </si>
+  <si>
+    <t>O tempo estimado de ressuprimento é de 75 dias para itens em Registro de Preços (RP) e de 90 dias para itens adquiridos via dispensa de licitação.</t>
+  </si>
+  <si>
+    <t>Qual a periodicidade da programação trimestral de itens em RP?</t>
+  </si>
+  <si>
+    <t>A elaboração da programação trimestral para itens em Registro de Preços ocorre mensalmente, especificamente no dia 15 de cada mês.</t>
+  </si>
+  <si>
+    <t>Quais são as listas do novo vínculo CAJ-ADMINISTRATIVO no SIGAF?</t>
+  </si>
+  <si>
+    <t>O vínculo está estruturado em três listas específicas no sistema: Termolábeis, Secos e Portaria 344.</t>
+  </si>
+  <si>
+    <t>Atendimento de Pacientes Novos</t>
+  </si>
+  <si>
+    <t>Como é feito o atendimento de pacientes novos quando há estoque disponível?</t>
+  </si>
+  <si>
+    <t>Deve-se verificar a cobertura do estoque atual. Caso seja suficiente para a inclusão, informa-se que o paciente pode ser atendido imediatamente.</t>
+  </si>
+  <si>
+    <t>É possível aumentar a quantidade de um processo de aquisição em andamento para atender um novo paciente?</t>
+  </si>
+  <si>
+    <t>Sim. Se o estágio do processo permitir, ele deve ser reaberto para inclusão da solicitação de aumento do quantitativo no ETP, sendo posteriormente enviado para assinatura da coordenação da CAJ.</t>
+  </si>
+  <si>
+    <t>O que fazer se o estoque for insuficiente e houver Ata de Registro de Preços vigente?</t>
+  </si>
+  <si>
+    <t>Verifica-se se há aquisição em andamento com quantitativo suficiente para o novo paciente. Caso contrário, solicita-se um novo saque da ata vigente.</t>
+  </si>
+  <si>
+    <t>O que ocorre se uma aquisição em andamento já tiver proposta vencedora e houver um novo paciente?</t>
+  </si>
+  <si>
+    <t>Não é mais possível alterar o processo atual. Nesse cenário, deve-se iniciar um novo processo de aquisição exclusivo para atender os pacientes novos.</t>
+  </si>
+  <si>
+    <t>Qual a cobertura mínima necessária para incluir um novo paciente em uma aquisição em andamento sem Ata vigente?</t>
+  </si>
+  <si>
+    <t>A nova cobertura de estoque, considerando o aumento do consumo, deve ser de no mínimo 90 dias para garantir que não haja impacto no atendimento dos pacientes antigos.</t>
+  </si>
+  <si>
+    <t>Canabidiol</t>
+  </si>
+  <si>
+    <t>Como é feita a solicitação de estoque regulador de Canabidiol pelo CRER?</t>
+  </si>
+  <si>
+    <t>A unidade avalia a demanda, realiza o pedido à CAJ via SIGAF na lista 'Portaria 344' e abre um processo no SEI informando o respectivo número do pedido.</t>
+  </si>
+  <si>
+    <t>Quais documentos são necessários para cadastrar um paciente de Canabidiol na CAJ?</t>
+  </si>
+  <si>
+    <t>São necessários os documentos pessoais (ID, Cartão SUS, Comprovante de Residência), relatório médico, Ficha de Encaminhamento preenchida e o despacho de deferimento do CRER.</t>
+  </si>
+  <si>
+    <t>Qual o tipo de receituário exigido para prescrição de Canabidiol?</t>
+  </si>
+  <si>
+    <t>Para Canabidiol isolado ou com até 0,2% de THC, exige-se receituário branco de controle especial em duas vias. Acima de 0,2% de THC, exige-se receituário tipo B (azul) com numeração controlada.</t>
+  </si>
+  <si>
+    <t>Controle de Validade e Perdas</t>
+  </si>
+  <si>
+    <t>O que fazer com medicamentos sem demanda com validade superior a 120 dias?</t>
+  </si>
+  <si>
+    <t>Pode-se realizar a permuta com o CEAF/CBAF, unidades da rede SESAB ou outras instituições públicas estaduais e externas para evitar o vencimento sem uso.</t>
+  </si>
+  <si>
+    <t>Qual a diferença entre permuta e doação no controle de perdas?</t>
+  </si>
+  <si>
+    <t>A permuta busca a troca por itens equivalentes para evitar prejuízo financeiro. A doação ocorre quando o item tem validade inferior a 120 dias e não há demanda interna, visando o uso antes do vencimento.</t>
+  </si>
+  <si>
+    <t>Qual o prazo mínimo de validade para aceitar a devolução de um medicamento por uma unidade?</t>
+  </si>
+  <si>
+    <t>O medicamento deve apresentar validade superior a 120 dias, exceto em casos específicos avaliados pelo setor de monitoramento.</t>
+  </si>
+  <si>
+    <t>Quais documentos devem compor o processo SEI mensal de controle de perdas?</t>
+  </si>
+  <si>
+    <t>O processo deve conter ofícios de tratativas, e-mails, termos de doação/permuta, notas de faturamento, histórico dos itens e o relatório de itens vencidos.</t>
+  </si>
+  <si>
+    <t>Quais situações podem gerar perda de estoque por prazo de validade?</t>
+  </si>
+  <si>
+    <t>As perdas podem ocorrer por óbito do paciente, suspensão de tratamento, não comparecimento para retirada ou atendimento por outras vias, como depósitos judiciais.</t>
+  </si>
+  <si>
+    <t>Depósito Judicial</t>
+  </si>
+  <si>
+    <t>Por que um processo de aquisição pode se tornar depósito judicial?</t>
+  </si>
+  <si>
+    <t>Isso ocorre quando não há sucesso na dispensa direta entre fornecedores, quando não existe Registro de Preços ativo ou por determinação específica do Superintendente.</t>
+  </si>
+  <si>
+    <t>Fluxo Operacional</t>
+  </si>
+  <si>
+    <t>A CAJ realiza atendimentos retroativos?</t>
+  </si>
+  <si>
+    <t>Não. O pedido de pendência deve ser efetuado exclusivamente para o mês de competência vigente ou para o mês subsequente.</t>
+  </si>
+  <si>
+    <t>Como proceder em caso de canetas permanentes de insulina com defeito?</t>
+  </si>
+  <si>
+    <t>O paciente entrega a caneta na unidade; o farmacêutico avalia se há erro de manuseio ou defeito técnico, notifica no Notivisa e solicita o recolhimento à CEFARBA com cópia para a CAJ.</t>
+  </si>
+  <si>
+    <t>Em que situações deve-se informar o óbito ou suspensão de tratamento à CAJ?</t>
+  </si>
+  <si>
+    <t>Sempre que houver mudança no status do tratamento, a unidade deve informar via e-mail (dasf.caj@saude.ba.gov.br) para que o setor de atendimento inative o cadastro no SIGAF.</t>
+  </si>
+  <si>
+    <t>O que é um 'Pedido de Pendência'?</t>
+  </si>
+  <si>
+    <t>É uma solicitação formal feita exclusivamente pela CAJ para regularizar falhas no envio (faturamento parcial ou zerado) decorrentes de falta de estoque ou erros operacionais.</t>
+  </si>
+  <si>
+    <t>Qual o período para realização do Pedido Complementar pelas unidades?</t>
+  </si>
+  <si>
+    <t>O Pedido Complementar deve ser realizado pelas unidades no período do dia 1º ao dia 15 de cada mês.</t>
+  </si>
+  <si>
+    <t>Qual o prazo para unidades fora de Salvador realizarem pedidos de pendência?</t>
+  </si>
+  <si>
+    <t>As unidades devem realizar a solicitação até o dia 20 de cada mês para incluir o pedido mensal anterior e o vigente.</t>
+  </si>
+  <si>
+    <t>Quais documentos devem acompanhar o primeiro atendimento do medicamento Daratumumabe?</t>
+  </si>
+  <si>
+    <t>O setor de cadastro deve registrar no sistema a data do primeiro atendimento, o número do atendimento e atualizar o campo 'Data Próximo Atendimento'.</t>
+  </si>
+  <si>
+    <t>Gestão de Processos</t>
+  </si>
+  <si>
+    <t>Qual a vantagem de utilizar a planilha do Microsoft Lists no atendimento?</t>
+  </si>
+  <si>
+    <t>A ferramenta permite o controle automatizado da data de retorno, facilita a filtragem de pacientes ativos e oferece uma visão centralizada em tempo real para o monitoramento.</t>
+  </si>
+  <si>
+    <t>Qual o papel do setor de Monitoramento do 1º Atendimento?</t>
+  </si>
+  <si>
+    <t>O setor verifica diariamente a entrada de medicamentos na CEFARBA para garantir que pacientes recém-cadastrados iniciem o tratamento imediatamente.</t>
+  </si>
+  <si>
+    <t>Judicialização</t>
+  </si>
+  <si>
+    <t>O Estado é obrigado a fornecer medicamentos experimentais?</t>
+  </si>
+  <si>
+    <t>Conforme o Tema 500 do STF, em regra geral, o Estado não é obrigado a fornecer medicamentos experimentais sem registro na Anvisa, salvo em casos excepcionais previstos em lei.</t>
+  </si>
+  <si>
+    <t>O que definiu o Tema 1234 do STF sobre competência?</t>
+  </si>
+  <si>
+    <t>Demandas de medicamentos não incorporados com valor anual ≥ 210 salários mínimos tramitam na Justiça Federal contra a União. Valores menores tramitam na Justiça Estadual contra o Estado.</t>
+  </si>
+  <si>
+    <t>Legislação de Licitações</t>
+  </si>
+  <si>
+    <t>Qual o prazo mínimo para apresentação de propostas em um pregão para aquisição de bens?</t>
+  </si>
+  <si>
+    <t>O prazo mínimo é de 8 dias úteis, contados a partir da data de divulgação do edital.</t>
+  </si>
+  <si>
+    <t>Qual o valor limite para dispensa de licitação para compras e outros serviços (Art. 75, II)?</t>
+  </si>
+  <si>
+    <t>O valor limite original de R50.000,00foiatualizadoparaR 54.020,41 de acordo com o Decreto nº 10.922/2021.</t>
+  </si>
+  <si>
+    <t>Quais são as modalidades de licitação previstas na Lei nº 14.133/2021?</t>
+  </si>
+  <si>
+    <t>As modalidades previstas são: Pregão, concorrência, concurso, leilão e diálogo competitivo.</t>
+  </si>
+  <si>
+    <t>Normas de Prescrição</t>
+  </si>
+  <si>
+    <t>O que é exigido para diagnosticar LADA em pacientes acima de 30 anos?</t>
+  </si>
+  <si>
+    <t>É necessária a comprovação de dosagem de peptídeo C reduzido e a positividade de pelo menos um marcador de autoimunidade (ex: Anti-GAD ou Anti-Ilhota).</t>
+  </si>
+  <si>
+    <t>Qual a norma para prescrição de medicamentos no âmbito do SUS?</t>
+  </si>
+  <si>
+    <t>As prescrições devem adotar obrigatoriamente a Denominação Comum Brasileira (DCB) ou, na sua ausência, a Denominação Comum Internacional (DCI).</t>
+  </si>
+  <si>
+    <t>Quais os critérios para manutenção do tratamento com análogos de insulina tipo 1?</t>
+  </si>
+  <si>
+    <t>O paciente deve comprovar automonitorização, acompanhamento regular e apresentar, nos últimos 6 meses, meta glicêmica atingida, redução de 0,5% na HbA1c ou melhora de hipoglicemias.</t>
+  </si>
+  <si>
+    <t>Atendimento</t>
+  </si>
+  <si>
+    <t>O que deve ser feito após a conclusão de todas as etapas de um tratamento com Daratumumabe?</t>
+  </si>
+  <si>
+    <t>O setor de atendimento deve informar o Monitoramento por e-mail para que a inativação seja devidamente comunicada ao Núcleo Jurídico.</t>
+  </si>
+  <si>
+    <t>Processos SEI</t>
+  </si>
+  <si>
+    <t>Como deve ser feita a identificação de pacientes nas embalagens de medicamentos?</t>
+  </si>
+  <si>
+    <t>É proibido escrever ou colar etiquetas diretamente na embalagem original. Devem ser utilizados recursos externos auxiliares para preservar a integridade da caixa.</t>
+  </si>
+  <si>
+    <t>Onde conferir a autenticidade de documentos assinados eletronicamente no SEI Bahia?</t>
+  </si>
+  <si>
+    <t>A conferência é feita no site oficial do SEI Bahia, utilizando o código verificador e o código CRC presentes no documento.</t>
+  </si>
+  <si>
+    <t>Ressarcimento Interfederativo</t>
+  </si>
+  <si>
+    <t>Em quais casos a União ressarcirá 100% do valor do medicamento?</t>
+  </si>
+  <si>
+    <t>Para medicamentos incorporados (Grupos 1A e 1B do CEAF/CESAF) ou medicamentos não incorporados com custo de tratamento anual igual ou superior a 210 salários mínimos.</t>
+  </si>
+  <si>
+    <t>O que é o Ressarcimento Interfederativo Judicial?</t>
+  </si>
+  <si>
+    <t>É o procedimento de repasse de valores entre entes federados que arcaram com o ônus de fornecer medicamentos por ordem judicial fora de sua responsabilidade pactuada.</t>
+  </si>
+  <si>
+    <t>Qual o prazo para a União realizar o pagamento dos ressarcimentos?</t>
+  </si>
+  <si>
+    <t>Para pedidos atuais, o prazo é de 2 a 3 anos. Para pedidos retroativos (entre 2018 e dezembro de 2024), o prazo de pagamento é de até 5 anos.</t>
+  </si>
+  <si>
+    <t>Quais documentos são necessários para solicitar o ressarcimento à União?</t>
+  </si>
+  <si>
+    <t>São exigidos: Ofício individualizado (NAJS), prescrição/relatório médico, decisão judicial, comprovante de gastos (NF ou empenho) e comprovante de entrega ao paciente.</t>
+  </si>
+  <si>
+    <t>Sistemas (SIGAF/BI)</t>
+  </si>
+  <si>
+    <t>Como identificar se um pedido autorizado já foi faturado pela CEFARBA?</t>
+  </si>
+  <si>
+    <t>Pesquisa-se o número do pedido no SIGAF; se faturado, o status constará como 'FATURADO' e o ícone da 'Nota de Fornecimento de Produto' estará visível.</t>
+  </si>
+  <si>
+    <t>O que fazer se o paciente não aparecer no Relatório CALAF Detalhe?</t>
+  </si>
+  <si>
+    <t>Deve-se verificar se há divergências cadastrais. Se o cadastro não existir, a unidade deve enviar um processo ao setor de cadastro da CAJ.</t>
+  </si>
+  <si>
+    <t>Onde as unidades dispensadoras devem realizar o pedido mensal de medicamentos?</t>
+  </si>
+  <si>
+    <t>O pedido deve ser feito no SIGAF através do caminho: Farmácia → Aquisição de Medicamentos → Programação de Medicamentos.</t>
+  </si>
+  <si>
+    <t>Para que serve o Relatório CALAF Detalhe no SIGAF?</t>
+  </si>
+  <si>
+    <t>Serve para validar se o pedido da unidade é compatível com o cadastro do paciente, verificando quantidade, frequência e se o status está ativo.</t>
+  </si>
+  <si>
+    <t>Quais os tipos de erros comuns detectados no BI da CAJ?</t>
+  </si>
+  <si>
+    <t>Os erros frequentes incluem: arquivo na pasta incorreta, pastas vazias, erros em formatos de data (ex: 00/00/0000) e valores duplicados na tabela dicionário.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,13 +431,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -88,12 +523,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:C7" totalsRowShown="0">
-  <autoFilter ref="A1:C7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:C51" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:C51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Categoria"/>
-    <tableColumn id="2" name="Pergunta"/>
-    <tableColumn id="3" name="Resposta"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Categoria" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Pergunta" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Resposta" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -361,24 +796,574 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/faq.xlsx
+++ b/faq.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lcreis\Documents\GitHub\faq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD83281-BCE1-4B32-8C29-EB64F156A667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940F64E9-D063-47F7-9B61-F4048ACECB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2490" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -38,15 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
   <si>
-    <t>Categoria</t>
-  </si>
-  <si>
-    <t>Pergunta</t>
-  </si>
-  <si>
-    <t>Resposta</t>
-  </si>
-  <si>
     <t>Acesso a Medicamentos</t>
   </si>
   <si>
@@ -390,19 +381,34 @@
   </si>
   <si>
     <t>Os erros frequentes incluem: arquivo na pasta incorreta, pastas vazias, erros em formatos de data (ex: 00/00/0000) e valores duplicados na tabela dicionário.</t>
+  </si>
+  <si>
+    <t>categoria</t>
+  </si>
+  <si>
+    <t>pergunta</t>
+  </si>
+  <si>
+    <t>resposta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -431,8 +437,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -523,12 +530,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:C51" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:C51" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:C51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Categoria" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Pergunta" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Resposta" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="categoria" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="pergunta" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="resposta" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -806,564 +813,564 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+      <c r="A1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C31" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="C33" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="C35" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="C38" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="C42" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="C44" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
